--- a/site/exports/dlut-math.xlsx
+++ b/site/exports/dlut-math.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -453,8 +453,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="37.8" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -569,10 +569,64 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>李风泉</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>数学科学学院</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/2003011090/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Official biography supports partial institutional association; independent directory and realtime employment unverified.；Study endpoints do not establish award dates; explicit award years only where stated.；Own supervisor names not retained; supervisor job title does not identify own mentors.；Selected works are source-reported; complete authorship/order, publisher metadata and full texts unverified.；Necessary retained excerpts only; no original HTTP or complete page certification.；Publication-list URL deduplication was after native-link resolution; initial names/profile URLs checked before body read.；Publication-list excerpts are retained selected fragments with omitted interleaved metadata; their locators mention ellipsis marks but the retained strings contain no ellipsis. Contiguous verbatim quotation and full author order are not authenticated.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K3"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -584,7 +638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -601,7 +655,7 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="58.8" customWidth="1" min="15" max="15"/>
+    <col width="65" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="65" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
@@ -666,7 +720,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1103,8 +1157,264 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>李风泉</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>学士</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>曲阜师范大学</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1990-09</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1992-07</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/2003011090/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>李风泉</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>兰州大学</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1992-09</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1995-07</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（学位获授日期）：1995</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/2003011090/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>李风泉</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1995-09</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1998-07</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（学位获授日期）：1998</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/2003011090/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>李风泉</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/2003011090/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S7"/>
+  <autoFilter ref="A1:S11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -1112,6 +1422,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1214,7 +1528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1225,8 +1539,8 @@
     <col width="44.8" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
-    <col width="58.8" customWidth="1" min="9" max="9"/>
-    <col width="44.8" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
@@ -1405,8 +1719,116 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>李风泉</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Average Shadowing Property and Asymptotic Average Shadowing Property of Linear Dynamical Systems</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/2003011090/zh_CN/lwcg/731546/list/index.htm</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>journal_article_as_official_list</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/2003011090/zh_CN/lwcg/731546/list/index.htm</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源书目信息（卷）：29；来源书目信息（期）：12；来源书目信息（person_name_in_listing）：Li, Fengquan</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>李风泉</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Modified Laplace variational iteration method for solving fourth-order parabolic partial differential equation with variable coefficients</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/2003011090/zh_CN/lwcg/731546/list/index.htm</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>journal_article_as_official_list</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/2003011090/zh_CN/lwcg/731546/list/index.htm</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源书目信息（卷）：78；来源书目信息（期）：6；来源书目信息（页码）：2052-2062；来源书目信息（person_name_in_listing）：Li, Fengquan</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -1414,6 +1836,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1425,14 +1851,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30.8" customWidth="1" min="2" max="2"/>
+    <col width="64.39999999999999" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1540,11 +1966,87 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>李风泉</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-dlut-lifengquan-s001-90312f7c4603</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/2003011090/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T05:45:35Z</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>李风泉</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-dlut-lifengquan-s002-43613c94034c</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/2003011090/zh_CN/lwcg/731546/list/index.htm</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T05:45:38Z</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/exports/dlut-math.xlsx
+++ b/site/exports/dlut-math.xlsx
@@ -1259,7 +1259,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L9" s="2" t="b">
@@ -1326,7 +1326,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L10" s="2" t="b">
